--- a/Excel/Avg/Rata-rata-32.xlsx
+++ b/Excel/Avg/Rata-rata-32.xlsx
@@ -620,22 +620,22 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>0.004502400000000001</v>
+        <v>0.0052123</v>
       </c>
       <c r="C2">
-        <v>0.0030006</v>
+        <v>0.0034918</v>
       </c>
       <c r="D2">
-        <v>0.0025612</v>
+        <v>0.0029867</v>
       </c>
       <c r="E2">
-        <v>0.003805100000000001</v>
+        <v>0.0044323</v>
       </c>
       <c r="F2">
-        <v>0.00583</v>
+        <v>0.006732200000000001</v>
       </c>
       <c r="G2">
-        <v>0.003939860000000001</v>
+        <v>0.00457106</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -643,22 +643,22 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>0.0015549</v>
+        <v>0.0017982</v>
       </c>
       <c r="C3">
-        <v>0.0013493</v>
+        <v>0.0014744</v>
       </c>
       <c r="D3">
-        <v>0.0010061</v>
+        <v>0.0011763</v>
       </c>
       <c r="E3">
-        <v>0.001183</v>
+        <v>0.0022138</v>
       </c>
       <c r="F3">
-        <v>0.0009848999999999999</v>
+        <v>0.0011237</v>
       </c>
       <c r="G3">
-        <v>0.00121564</v>
+        <v>0.00155728</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -666,22 +666,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>0.0041621</v>
+        <v>0.0048364</v>
       </c>
       <c r="C4">
-        <v>0.0021858</v>
+        <v>0.0024186</v>
       </c>
       <c r="D4">
-        <v>0.0015832</v>
+        <v>0.0018873</v>
       </c>
       <c r="E4">
-        <v>0.0012577</v>
+        <v>0.0013845</v>
       </c>
       <c r="F4">
-        <v>0.0012056</v>
+        <v>0.0014852</v>
       </c>
       <c r="G4">
-        <v>0.00207888</v>
+        <v>0.0024024</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -689,22 +689,22 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>0.0041268</v>
+        <v>0.0047662</v>
       </c>
       <c r="C5">
-        <v>0.0023919</v>
+        <v>0.002888</v>
       </c>
       <c r="D5">
-        <v>0.0020154</v>
+        <v>0.0027794</v>
       </c>
       <c r="E5">
-        <v>0.0026728</v>
+        <v>0.0030605</v>
       </c>
       <c r="F5">
-        <v>0.003659199999999999</v>
+        <v>0.0042629</v>
       </c>
       <c r="G5">
-        <v>0.00297322</v>
+        <v>0.0035514</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -712,22 +712,22 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>0.0019007</v>
+        <v>0.0022074</v>
       </c>
       <c r="C6">
-        <v>0.0010816</v>
+        <v>0.0012128</v>
       </c>
       <c r="D6">
-        <v>0.0013472</v>
+        <v>0.0016024</v>
       </c>
       <c r="E6">
-        <v>0.001398</v>
+        <v>0.0016371</v>
       </c>
       <c r="F6">
-        <v>0.0022631</v>
+        <v>0.0026451</v>
       </c>
       <c r="G6">
-        <v>0.00159812</v>
+        <v>0.00186096</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -735,22 +735,22 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>0.004393200000000001</v>
+        <v>0.0051764</v>
       </c>
       <c r="C7">
-        <v>0.0031369</v>
+        <v>0.0035412</v>
       </c>
       <c r="D7">
-        <v>0.0026337</v>
+        <v>0.003274</v>
       </c>
       <c r="E7">
-        <v>0.0038302</v>
+        <v>0.004492700000000001</v>
       </c>
       <c r="F7">
-        <v>0.0058693</v>
+        <v>0.0068039</v>
       </c>
       <c r="G7">
-        <v>0.00397266</v>
+        <v>0.00465764</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -758,22 +758,22 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>0.0044716</v>
+        <v>0.005303899999999999</v>
       </c>
       <c r="C8">
-        <v>0.0028988</v>
+        <v>0.0032988</v>
       </c>
       <c r="D8">
-        <v>0.0024175</v>
+        <v>0.0028619</v>
       </c>
       <c r="E8">
-        <v>0.0037454</v>
+        <v>0.004345</v>
       </c>
       <c r="F8">
-        <v>0.006962800000000001</v>
+        <v>0.0083018</v>
       </c>
       <c r="G8">
-        <v>0.00409922</v>
+        <v>0.00482228</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -781,22 +781,22 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>0.002411</v>
+        <v>0.0027551</v>
       </c>
       <c r="C9">
-        <v>0.0018497</v>
+        <v>0.0020647</v>
       </c>
       <c r="D9">
-        <v>0.0011968</v>
+        <v>0.0013994</v>
       </c>
       <c r="E9">
-        <v>0.0010988</v>
+        <v>0.0014024</v>
       </c>
       <c r="F9">
-        <v>0.0010075</v>
+        <v>0.0014745</v>
       </c>
       <c r="G9">
-        <v>0.00151276</v>
+        <v>0.00181922</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -804,22 +804,22 @@
         <v>15</v>
       </c>
       <c r="B10">
-        <v>0.0015907</v>
+        <v>0.0018491</v>
       </c>
       <c r="C10">
-        <v>0.0014367</v>
+        <v>0.0016864</v>
       </c>
       <c r="D10">
-        <v>0.0008747</v>
+        <v>0.0009841000000000001</v>
       </c>
       <c r="E10">
-        <v>0.0014929</v>
+        <v>0.0018964</v>
       </c>
       <c r="F10">
-        <v>0.0013165</v>
+        <v>0.0015424</v>
       </c>
       <c r="G10">
-        <v>0.0013423</v>
+        <v>0.00159168</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -827,22 +827,22 @@
         <v>16</v>
       </c>
       <c r="B11">
-        <v>0.0016557</v>
+        <v>0.0020731</v>
       </c>
       <c r="C11">
-        <v>0.0014064</v>
+        <v>0.0016905</v>
       </c>
       <c r="D11">
-        <v>0.0011001</v>
+        <v>0.0012663</v>
       </c>
       <c r="E11">
-        <v>0.0012741</v>
+        <v>0.0026886</v>
       </c>
       <c r="F11">
-        <v>0.0011617</v>
+        <v>0.0012085</v>
       </c>
       <c r="G11">
-        <v>0.0013196</v>
+        <v>0.0017854</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -850,22 +850,22 @@
         <v>17</v>
       </c>
       <c r="B12">
-        <v>0.0017736</v>
+        <v>0.0022314</v>
       </c>
       <c r="C12">
-        <v>0.0015202</v>
+        <v>0.001769</v>
       </c>
       <c r="D12">
-        <v>0.0010769</v>
+        <v>0.0012961</v>
       </c>
       <c r="E12">
-        <v>0.0013986</v>
+        <v>0.0019605</v>
       </c>
       <c r="F12">
-        <v>0.0011149</v>
+        <v>0.0013812</v>
       </c>
       <c r="G12">
-        <v>0.00137684</v>
+        <v>0.00172764</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -873,22 +873,22 @@
         <v>18</v>
       </c>
       <c r="B13">
-        <v>0.0043894</v>
+        <v>0.0049979</v>
       </c>
       <c r="C13">
-        <v>0.0023208</v>
+        <v>0.0025959</v>
       </c>
       <c r="D13">
-        <v>0.0017123</v>
+        <v>0.0019258</v>
       </c>
       <c r="E13">
-        <v>0.0013513</v>
+        <v>0.0014872</v>
       </c>
       <c r="F13">
-        <v>0.0013179</v>
+        <v>0.0015131</v>
       </c>
       <c r="G13">
-        <v>0.00221834</v>
+        <v>0.00250398</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -896,22 +896,22 @@
         <v>19</v>
       </c>
       <c r="B14">
-        <v>0.004524100000000001</v>
+        <v>0.0056787</v>
       </c>
       <c r="C14">
-        <v>0.0022897</v>
+        <v>0.0025619</v>
       </c>
       <c r="D14">
-        <v>0.0023418</v>
+        <v>0.0026839</v>
       </c>
       <c r="E14">
-        <v>0.001317</v>
+        <v>0.0015003</v>
       </c>
       <c r="F14">
-        <v>0.0013389</v>
+        <v>0.0019257</v>
       </c>
       <c r="G14">
-        <v>0.0023623</v>
+        <v>0.0028701</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -919,22 +919,22 @@
         <v>20</v>
       </c>
       <c r="B15">
-        <v>0.0054286</v>
+        <v>0.0063464</v>
       </c>
       <c r="C15">
-        <v>0.0029753</v>
+        <v>0.0032645</v>
       </c>
       <c r="D15">
-        <v>0.0018718</v>
+        <v>0.0021671</v>
       </c>
       <c r="E15">
-        <v>0.0013331</v>
+        <v>0.001542</v>
       </c>
       <c r="F15">
-        <v>0.0024359</v>
+        <v>0.002881</v>
       </c>
       <c r="G15">
-        <v>0.00280894</v>
+        <v>0.0032402</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -942,22 +942,22 @@
         <v>21</v>
       </c>
       <c r="B16">
-        <v>0.0042241</v>
+        <v>0.004879700000000001</v>
       </c>
       <c r="C16">
-        <v>0.0025499</v>
+        <v>0.0030002</v>
       </c>
       <c r="D16">
-        <v>0.0021209</v>
+        <v>0.002520499999999999</v>
       </c>
       <c r="E16">
-        <v>0.0027619</v>
+        <v>0.0032083</v>
       </c>
       <c r="F16">
-        <v>0.0037637</v>
+        <v>0.004814000000000001</v>
       </c>
       <c r="G16">
-        <v>0.0030841</v>
+        <v>0.00368454</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -965,22 +965,22 @@
         <v>22</v>
       </c>
       <c r="B17">
-        <v>0.0043771</v>
+        <v>0.0051079</v>
       </c>
       <c r="C17">
-        <v>0.003556300000000001</v>
+        <v>0.0041226</v>
       </c>
       <c r="D17">
-        <v>0.0022373</v>
+        <v>0.0024694</v>
       </c>
       <c r="E17">
-        <v>0.0028879</v>
+        <v>0.0033714</v>
       </c>
       <c r="F17">
-        <v>0.0032192</v>
+        <v>0.003727900000000001</v>
       </c>
       <c r="G17">
-        <v>0.00325556</v>
+        <v>0.00375984</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -988,22 +988,22 @@
         <v>23</v>
       </c>
       <c r="B18">
-        <v>0.0014403</v>
+        <v>0.0017055</v>
       </c>
       <c r="C18">
-        <v>0.0009771999999999999</v>
+        <v>0.001193</v>
       </c>
       <c r="D18">
-        <v>0.0009649000000000001</v>
+        <v>0.0011193</v>
       </c>
       <c r="E18">
-        <v>0.0009571</v>
+        <v>0.0011335</v>
       </c>
       <c r="F18">
-        <v>0.0016268</v>
+        <v>0.0020559</v>
       </c>
       <c r="G18">
-        <v>0.00119326</v>
+        <v>0.00144144</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1011,22 +1011,22 @@
         <v>24</v>
       </c>
       <c r="B19">
-        <v>0.0014727</v>
+        <v>0.0017059</v>
       </c>
       <c r="C19">
-        <v>0.0010382</v>
+        <v>0.0010883</v>
       </c>
       <c r="D19">
-        <v>0.0006833000000000001</v>
+        <v>0.0007889</v>
       </c>
       <c r="E19">
-        <v>0.0006669</v>
+        <v>0.0008689</v>
       </c>
       <c r="F19">
-        <v>0.0010477</v>
+        <v>0.0012234</v>
       </c>
       <c r="G19">
-        <v>0.0009817599999999999</v>
+        <v>0.00113508</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1034,22 +1034,22 @@
         <v>25</v>
       </c>
       <c r="B20">
-        <v>0.0017755</v>
+        <v>0.0020236</v>
       </c>
       <c r="C20">
-        <v>0.0011515</v>
+        <v>0.0014557</v>
       </c>
       <c r="D20">
-        <v>0.0012193</v>
+        <v>0.0014396</v>
       </c>
       <c r="E20">
-        <v>0.0011866</v>
+        <v>0.0013525</v>
       </c>
       <c r="F20">
-        <v>0.0018773</v>
+        <v>0.0021154</v>
       </c>
       <c r="G20">
-        <v>0.00144204</v>
+        <v>0.00167736</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1057,22 +1057,22 @@
         <v>26</v>
       </c>
       <c r="B21">
-        <v>0.0019664</v>
+        <v>0.0022968</v>
       </c>
       <c r="C21">
-        <v>0.0012167</v>
+        <v>0.0012578</v>
       </c>
       <c r="D21">
-        <v>0.0014165</v>
+        <v>0.0016262</v>
       </c>
       <c r="E21">
-        <v>0.0014488</v>
+        <v>0.0017905</v>
       </c>
       <c r="F21">
-        <v>0.002819700000000001</v>
+        <v>0.0025678</v>
       </c>
       <c r="G21">
-        <v>0.00177362</v>
+        <v>0.00190782</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1080,22 +1080,22 @@
         <v>27</v>
       </c>
       <c r="B22">
-        <v>0.0021722</v>
+        <v>0.0023389</v>
       </c>
       <c r="C22">
-        <v>0.0012822</v>
+        <v>0.0012539</v>
       </c>
       <c r="D22">
-        <v>0.0013659</v>
+        <v>0.0016018</v>
       </c>
       <c r="E22">
-        <v>0.0013975</v>
+        <v>0.0016966</v>
       </c>
       <c r="F22">
-        <v>0.0027457</v>
+        <v>0.0025155</v>
       </c>
       <c r="G22">
-        <v>0.0017927</v>
+        <v>0.00188134</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1103,22 +1103,22 @@
         <v>28</v>
       </c>
       <c r="B23">
-        <v>0.0045512</v>
+        <v>0.0052702</v>
       </c>
       <c r="C23">
-        <v>0.0030051</v>
+        <v>0.003424299999999999</v>
       </c>
       <c r="D23">
-        <v>0.002568</v>
+        <v>0.0030026</v>
       </c>
       <c r="E23">
-        <v>0.0038284</v>
+        <v>0.004545700000000001</v>
       </c>
       <c r="F23">
-        <v>0.007072299999999999</v>
+        <v>0.008379399999999999</v>
       </c>
       <c r="G23">
-        <v>0.004205</v>
+        <v>0.00492444</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1126,22 +1126,22 @@
         <v>29</v>
       </c>
       <c r="B24">
-        <v>0.0025243</v>
+        <v>0.003232899999999999</v>
       </c>
       <c r="C24">
-        <v>0.0019467</v>
+        <v>0.0021482</v>
       </c>
       <c r="D24">
-        <v>0.0013277</v>
+        <v>0.0015695</v>
       </c>
       <c r="E24">
-        <v>0.0012131</v>
+        <v>0.00139</v>
       </c>
       <c r="F24">
-        <v>0.0010833</v>
+        <v>0.0014281</v>
       </c>
       <c r="G24">
-        <v>0.00161902</v>
+        <v>0.00195374</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1149,22 +1149,22 @@
         <v>30</v>
       </c>
       <c r="B25">
-        <v>0.002314</v>
+        <v>0.0031798</v>
       </c>
       <c r="C25">
-        <v>0.0020586</v>
+        <v>0.0022636</v>
       </c>
       <c r="D25">
-        <v>0.0014211</v>
+        <v>0.0016908</v>
       </c>
       <c r="E25">
-        <v>0.0012131</v>
+        <v>0.0014048</v>
       </c>
       <c r="F25">
-        <v>0.0010694</v>
+        <v>0.0015329</v>
       </c>
       <c r="G25">
-        <v>0.00161524</v>
+        <v>0.00201438</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1172,22 +1172,22 @@
         <v>31</v>
       </c>
       <c r="B26">
-        <v>0.0025884</v>
+        <v>0.0029792</v>
       </c>
       <c r="C26">
-        <v>0.0030069</v>
+        <v>0.0033494</v>
       </c>
       <c r="D26">
-        <v>0.0014182</v>
+        <v>0.0016395</v>
       </c>
       <c r="E26">
-        <v>0.0012749</v>
+        <v>0.0014501</v>
       </c>
       <c r="F26">
-        <v>0.0022269</v>
+        <v>0.0026163</v>
       </c>
       <c r="G26">
-        <v>0.00210306</v>
+        <v>0.0024069</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1195,22 +1195,22 @@
         <v>32</v>
       </c>
       <c r="B27">
-        <v>0.0017126</v>
+        <v>0.0019934</v>
       </c>
       <c r="C27">
-        <v>0.0016725</v>
+        <v>0.0017889</v>
       </c>
       <c r="D27">
-        <v>0.0009774000000000002</v>
+        <v>0.0011242</v>
       </c>
       <c r="E27">
-        <v>0.0015437</v>
+        <v>0.0018259</v>
       </c>
       <c r="F27">
-        <v>0.001496</v>
+        <v>0.0016273</v>
       </c>
       <c r="G27">
-        <v>0.00148044</v>
+        <v>0.00167194</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1218,22 +1218,22 @@
         <v>33</v>
       </c>
       <c r="B28">
-        <v>0.0017038</v>
+        <v>0.0020341</v>
       </c>
       <c r="C28">
-        <v>0.0015914</v>
+        <v>0.0018891</v>
       </c>
       <c r="D28">
-        <v>0.0009577</v>
+        <v>0.0011182</v>
       </c>
       <c r="E28">
-        <v>0.0015867</v>
+        <v>0.001885</v>
       </c>
       <c r="F28">
-        <v>0.0014883</v>
+        <v>0.0017378</v>
       </c>
       <c r="G28">
-        <v>0.00146558</v>
+        <v>0.00173284</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1241,22 +1241,22 @@
         <v>34</v>
       </c>
       <c r="B29">
-        <v>0.0018871</v>
+        <v>0.0022085</v>
       </c>
       <c r="C29">
-        <v>0.0015942</v>
+        <v>0.0018809</v>
       </c>
       <c r="D29">
-        <v>0.001172</v>
+        <v>0.0013481</v>
       </c>
       <c r="E29">
-        <v>0.0014827</v>
+        <v>0.0018153</v>
       </c>
       <c r="F29">
-        <v>0.0012386</v>
+        <v>0.0016566</v>
       </c>
       <c r="G29">
-        <v>0.00147492</v>
+        <v>0.00178188</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1264,22 +1264,22 @@
         <v>35</v>
       </c>
       <c r="B30">
-        <v>0.004606399999999999</v>
+        <v>0.005793400000000001</v>
       </c>
       <c r="C30">
-        <v>0.0024127</v>
+        <v>0.0028081</v>
       </c>
       <c r="D30">
-        <v>0.0023507</v>
+        <v>0.0029354</v>
       </c>
       <c r="E30">
-        <v>0.001398</v>
+        <v>0.0015936</v>
       </c>
       <c r="F30">
-        <v>0.0014816</v>
+        <v>0.0018583</v>
       </c>
       <c r="G30">
-        <v>0.002449879999999999</v>
+        <v>0.00299776</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1287,22 +1287,22 @@
         <v>36</v>
       </c>
       <c r="B31">
-        <v>0.0054957</v>
+        <v>0.006352399999999999</v>
       </c>
       <c r="C31">
-        <v>0.0030467</v>
+        <v>0.0034339</v>
       </c>
       <c r="D31">
-        <v>0.0019174</v>
+        <v>0.0022631</v>
       </c>
       <c r="E31">
-        <v>0.0014379</v>
+        <v>0.0018449</v>
       </c>
       <c r="F31">
-        <v>0.0025982</v>
+        <v>0.0028983</v>
       </c>
       <c r="G31">
-        <v>0.00289918</v>
+        <v>0.00335852</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1310,22 +1310,22 @@
         <v>37</v>
       </c>
       <c r="B32">
-        <v>0.0056181</v>
+        <v>0.0065389</v>
       </c>
       <c r="C32">
-        <v>0.0029675</v>
+        <v>0.0037297</v>
       </c>
       <c r="D32">
-        <v>0.0019461</v>
+        <v>0.0021753</v>
       </c>
       <c r="E32">
-        <v>0.0013855</v>
+        <v>0.0016575</v>
       </c>
       <c r="F32">
-        <v>0.0014011</v>
+        <v>0.0016025</v>
       </c>
       <c r="G32">
-        <v>0.00266366</v>
+        <v>0.00314078</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1333,22 +1333,22 @@
         <v>38</v>
       </c>
       <c r="B33">
-        <v>0.004460800000000001</v>
+        <v>0.0054806</v>
       </c>
       <c r="C33">
-        <v>0.004153</v>
+        <v>0.0042565</v>
       </c>
       <c r="D33">
-        <v>0.0022172</v>
+        <v>0.0026255</v>
       </c>
       <c r="E33">
-        <v>0.0029744</v>
+        <v>0.0034678</v>
       </c>
       <c r="F33">
-        <v>0.0033947</v>
+        <v>0.0038899</v>
       </c>
       <c r="G33">
-        <v>0.00344002</v>
+        <v>0.003944060000000001</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1356,22 +1356,22 @@
         <v>39</v>
       </c>
       <c r="B34">
-        <v>0.0012852</v>
+        <v>0.0014777</v>
       </c>
       <c r="C34">
-        <v>0.001106</v>
+        <v>0.0013242</v>
       </c>
       <c r="D34">
-        <v>0.0007581</v>
+        <v>0.0008721000000000001</v>
       </c>
       <c r="E34">
-        <v>0.0009783999999999999</v>
+        <v>0.0011587</v>
       </c>
       <c r="F34">
-        <v>0.0020597</v>
+        <v>0.0023138</v>
       </c>
       <c r="G34">
-        <v>0.00123748</v>
+        <v>0.0014293</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1379,22 +1379,22 @@
         <v>40</v>
       </c>
       <c r="B35">
-        <v>0.0008677000000000001</v>
+        <v>0.0010417</v>
       </c>
       <c r="C35">
-        <v>0.0010366</v>
+        <v>0.0012193</v>
       </c>
       <c r="D35">
-        <v>0.0009082</v>
+        <v>0.0010289</v>
       </c>
       <c r="E35">
-        <v>0.0013138</v>
+        <v>0.0014952</v>
       </c>
       <c r="F35">
-        <v>0.0020319</v>
+        <v>0.0022995</v>
       </c>
       <c r="G35">
-        <v>0.00123164</v>
+        <v>0.00141692</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1402,22 +1402,22 @@
         <v>41</v>
       </c>
       <c r="B36">
-        <v>0.0015038</v>
+        <v>0.0017345</v>
       </c>
       <c r="C36">
-        <v>0.0010701</v>
+        <v>0.0012212</v>
       </c>
       <c r="D36">
-        <v>0.0010177</v>
+        <v>0.0012315</v>
       </c>
       <c r="E36">
-        <v>0.0011502</v>
+        <v>0.0011508</v>
       </c>
       <c r="F36">
-        <v>0.0016802</v>
+        <v>0.0021393</v>
       </c>
       <c r="G36">
-        <v>0.0012844</v>
+        <v>0.00149546</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1425,22 +1425,22 @@
         <v>42</v>
       </c>
       <c r="B37">
-        <v>0.0011697</v>
+        <v>0.0017071</v>
       </c>
       <c r="C37">
-        <v>0.0012048</v>
+        <v>0.0011604</v>
       </c>
       <c r="D37">
-        <v>0.0008583999999999999</v>
+        <v>0.00122</v>
       </c>
       <c r="E37">
-        <v>0.0011378</v>
+        <v>0.0010805</v>
       </c>
       <c r="F37">
-        <v>0.0015293</v>
+        <v>0.0018892</v>
       </c>
       <c r="G37">
-        <v>0.00118</v>
+        <v>0.00141144</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1448,22 +1448,22 @@
         <v>43</v>
       </c>
       <c r="B38">
-        <v>0.0015409</v>
+        <v>0.0017727</v>
       </c>
       <c r="C38">
-        <v>0.001075</v>
+        <v>0.0011775</v>
       </c>
       <c r="D38">
-        <v>0.0007454</v>
+        <v>0.0008484</v>
       </c>
       <c r="E38">
-        <v>0.0007455</v>
+        <v>0.0008321</v>
       </c>
       <c r="F38">
-        <v>0.001101</v>
+        <v>0.0012614</v>
       </c>
       <c r="G38">
-        <v>0.00104156</v>
+        <v>0.00117842</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1471,22 +1471,22 @@
         <v>44</v>
       </c>
       <c r="B39">
-        <v>0.0014839</v>
+        <v>0.0017366</v>
       </c>
       <c r="C39">
-        <v>0.0010607</v>
+        <v>0.0011443</v>
       </c>
       <c r="D39">
-        <v>0.0006773</v>
+        <v>0.0008433999999999999</v>
       </c>
       <c r="E39">
-        <v>0.0006692</v>
+        <v>0.0008265</v>
       </c>
       <c r="F39">
-        <v>0.0010562</v>
+        <v>0.0012193</v>
       </c>
       <c r="G39">
-        <v>0.0009894599999999999</v>
+        <v>0.00115402</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1494,22 +1494,22 @@
         <v>45</v>
       </c>
       <c r="B40">
-        <v>0.0015761</v>
+        <v>0.0018559</v>
       </c>
       <c r="C40">
-        <v>0.0010706</v>
+        <v>0.0013411</v>
       </c>
       <c r="D40">
-        <v>0.0009492999999999999</v>
+        <v>0.0011759</v>
       </c>
       <c r="E40">
-        <v>0.000724</v>
+        <v>0.0008111</v>
       </c>
       <c r="F40">
-        <v>0.0011575</v>
+        <v>0.0013633</v>
       </c>
       <c r="G40">
-        <v>0.0010955</v>
+        <v>0.00130946</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1517,22 +1517,22 @@
         <v>46</v>
       </c>
       <c r="B41">
-        <v>0.0018004</v>
+        <v>0.0020993</v>
       </c>
       <c r="C41">
-        <v>0.0012287</v>
+        <v>0.001422</v>
       </c>
       <c r="D41">
-        <v>0.0013071</v>
+        <v>0.0016311</v>
       </c>
       <c r="E41">
-        <v>0.0012535</v>
+        <v>0.0014402</v>
       </c>
       <c r="F41">
-        <v>0.0018902</v>
+        <v>0.002175499999999999</v>
       </c>
       <c r="G41">
-        <v>0.00149598</v>
+        <v>0.00175362</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1540,22 +1540,22 @@
         <v>47</v>
       </c>
       <c r="B42">
-        <v>0.0018184</v>
+        <v>0.0020842</v>
       </c>
       <c r="C42">
-        <v>0.001176</v>
+        <v>0.0013742</v>
       </c>
       <c r="D42">
-        <v>0.0012647</v>
+        <v>0.0015247</v>
       </c>
       <c r="E42">
-        <v>0.0012249</v>
+        <v>0.0013874</v>
       </c>
       <c r="F42">
-        <v>0.0023361</v>
+        <v>0.0021617</v>
       </c>
       <c r="G42">
-        <v>0.00156402</v>
+        <v>0.00170644</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1563,22 +1563,22 @@
         <v>48</v>
       </c>
       <c r="B43">
-        <v>0.0022073</v>
+        <v>0.0023383</v>
       </c>
       <c r="C43">
-        <v>0.0012118</v>
+        <v>0.0013294</v>
       </c>
       <c r="D43">
-        <v>0.0014257</v>
+        <v>0.0016979</v>
       </c>
       <c r="E43">
-        <v>0.0014654</v>
+        <v>0.0017797</v>
       </c>
       <c r="F43">
-        <v>0.0021946</v>
+        <v>0.0024993</v>
       </c>
       <c r="G43">
-        <v>0.00170096</v>
+        <v>0.00192892</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1586,22 +1586,22 @@
         <v>49</v>
       </c>
       <c r="B44">
-        <v>0.0024552</v>
+        <v>0.0030365</v>
       </c>
       <c r="C44">
-        <v>0.002117200000000001</v>
+        <v>0.0024169</v>
       </c>
       <c r="D44">
-        <v>0.0015562</v>
+        <v>0.0017889</v>
       </c>
       <c r="E44">
-        <v>0.0012957</v>
+        <v>0.001497</v>
       </c>
       <c r="F44">
-        <v>0.0012062</v>
+        <v>0.0016199</v>
       </c>
       <c r="G44">
-        <v>0.0017261</v>
+        <v>0.00207184</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1609,22 +1609,22 @@
         <v>50</v>
       </c>
       <c r="B45">
-        <v>0.0027221</v>
+        <v>0.0032014</v>
       </c>
       <c r="C45">
-        <v>0.0030012</v>
+        <v>0.0033321</v>
       </c>
       <c r="D45">
-        <v>0.0015082</v>
+        <v>0.0016664</v>
       </c>
       <c r="E45">
-        <v>0.0013593</v>
+        <v>0.0016488</v>
       </c>
       <c r="F45">
-        <v>0.0023509</v>
+        <v>0.0027802</v>
       </c>
       <c r="G45">
-        <v>0.00218834</v>
+        <v>0.00252578</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1632,22 +1632,22 @@
         <v>51</v>
       </c>
       <c r="B46">
-        <v>0.0027088</v>
+        <v>0.0031165</v>
       </c>
       <c r="C46">
-        <v>0.0030347</v>
+        <v>0.003618</v>
       </c>
       <c r="D46">
-        <v>0.001491</v>
+        <v>0.0017865</v>
       </c>
       <c r="E46">
-        <v>0.001308</v>
+        <v>0.001521</v>
       </c>
       <c r="F46">
-        <v>0.0012229</v>
+        <v>0.0014539</v>
       </c>
       <c r="G46">
-        <v>0.00195308</v>
+        <v>0.00229918</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1655,22 +1655,22 @@
         <v>52</v>
       </c>
       <c r="B47">
-        <v>0.0018246</v>
+        <v>0.002144</v>
       </c>
       <c r="C47">
-        <v>0.0017495</v>
+        <v>0.0020094</v>
       </c>
       <c r="D47">
-        <v>0.0010612</v>
+        <v>0.0012091</v>
       </c>
       <c r="E47">
-        <v>0.0016903</v>
+        <v>0.0019696</v>
       </c>
       <c r="F47">
-        <v>0.0015719</v>
+        <v>0.0019544</v>
       </c>
       <c r="G47">
-        <v>0.0015795</v>
+        <v>0.0018573</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1678,22 +1678,22 @@
         <v>53</v>
       </c>
       <c r="B48">
-        <v>0.0057332</v>
+        <v>0.006610100000000001</v>
       </c>
       <c r="C48">
-        <v>0.0030918</v>
+        <v>0.0038902</v>
       </c>
       <c r="D48">
-        <v>0.002034</v>
+        <v>0.0023631</v>
       </c>
       <c r="E48">
-        <v>0.0014552</v>
+        <v>0.0017811</v>
       </c>
       <c r="F48">
-        <v>0.0015338</v>
+        <v>0.0017364</v>
       </c>
       <c r="G48">
-        <v>0.0027696</v>
+        <v>0.00327618</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1701,22 +1701,22 @@
         <v>54</v>
       </c>
       <c r="B49">
-        <v>0.0013416</v>
+        <v>0.0015839</v>
       </c>
       <c r="C49">
-        <v>0.0011891</v>
+        <v>0.0014022</v>
       </c>
       <c r="D49">
-        <v>0.0008357</v>
+        <v>0.0009417</v>
       </c>
       <c r="E49">
-        <v>0.0014495</v>
+        <v>0.0012608</v>
       </c>
       <c r="F49">
-        <v>0.002099600000000001</v>
+        <v>0.0023436</v>
       </c>
       <c r="G49">
-        <v>0.0013831</v>
+        <v>0.00150644</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1724,22 +1724,22 @@
         <v>55</v>
       </c>
       <c r="B50">
-        <v>0.0014135</v>
+        <v>0.0016018</v>
       </c>
       <c r="C50">
-        <v>0.0013237</v>
+        <v>0.0013361</v>
       </c>
       <c r="D50">
-        <v>0.0009824</v>
+        <v>0.0010394</v>
       </c>
       <c r="E50">
-        <v>0.0013606</v>
+        <v>0.0012508</v>
       </c>
       <c r="F50">
-        <v>0.0016042</v>
+        <v>0.0023643</v>
       </c>
       <c r="G50">
-        <v>0.00133688</v>
+        <v>0.00151848</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1747,22 +1747,22 @@
         <v>56</v>
       </c>
       <c r="B51">
-        <v>0.0009419999999999999</v>
+        <v>0.0010819</v>
       </c>
       <c r="C51">
-        <v>0.0012639</v>
+        <v>0.0014769</v>
       </c>
       <c r="D51">
-        <v>0.0010714</v>
+        <v>0.0012701</v>
       </c>
       <c r="E51">
-        <v>0.00103</v>
+        <v>0.0012284</v>
       </c>
       <c r="F51">
-        <v>0.002155</v>
+        <v>0.0025185</v>
       </c>
       <c r="G51">
-        <v>0.00129246</v>
+        <v>0.00151516</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1770,22 +1770,22 @@
         <v>57</v>
       </c>
       <c r="B52">
-        <v>0.0009570000000000001</v>
+        <v>0.0011115</v>
       </c>
       <c r="C52">
-        <v>0.0010848</v>
+        <v>0.0012985</v>
       </c>
       <c r="D52">
-        <v>0.0009465000000000001</v>
+        <v>0.0011159</v>
       </c>
       <c r="E52">
-        <v>0.0014373</v>
+        <v>0.0015553</v>
       </c>
       <c r="F52">
-        <v>0.0021238</v>
+        <v>0.0023527</v>
       </c>
       <c r="G52">
-        <v>0.00130988</v>
+        <v>0.00148678</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1793,22 +1793,22 @@
         <v>58</v>
       </c>
       <c r="B53">
-        <v>0.0009595000000000001</v>
+        <v>0.0010628</v>
       </c>
       <c r="C53">
-        <v>0.0010539</v>
+        <v>0.0013032</v>
       </c>
       <c r="D53">
-        <v>0.0009337000000000002</v>
+        <v>0.0010561</v>
       </c>
       <c r="E53">
-        <v>0.000917</v>
+        <v>0.0015578</v>
       </c>
       <c r="F53">
-        <v>0.0016059</v>
+        <v>0.0023614</v>
       </c>
       <c r="G53">
-        <v>0.001094</v>
+        <v>0.00146826</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1816,22 +1816,22 @@
         <v>59</v>
       </c>
       <c r="B54">
-        <v>0.0012128</v>
+        <v>0.0017475</v>
       </c>
       <c r="C54">
-        <v>0.0012344</v>
+        <v>0.0012614</v>
       </c>
       <c r="D54">
-        <v>0.0009551000000000001</v>
+        <v>0.0012695</v>
       </c>
       <c r="E54">
-        <v>0.0011881</v>
+        <v>0.0011476</v>
       </c>
       <c r="F54">
-        <v>0.0015303</v>
+        <v>0.0019785</v>
       </c>
       <c r="G54">
-        <v>0.00122414</v>
+        <v>0.0014809</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1839,22 +1839,22 @@
         <v>60</v>
       </c>
       <c r="B55">
-        <v>0.0016622</v>
+        <v>0.0017847</v>
       </c>
       <c r="C55">
-        <v>0.0010424</v>
+        <v>0.0013992</v>
       </c>
       <c r="D55">
-        <v>0.0007915999999999999</v>
+        <v>0.0009354</v>
       </c>
       <c r="E55">
-        <v>0.0007592</v>
+        <v>0.0008328000000000001</v>
       </c>
       <c r="F55">
-        <v>0.001104</v>
+        <v>0.0012583</v>
       </c>
       <c r="G55">
-        <v>0.00107188</v>
+        <v>0.00124208</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1862,22 +1862,22 @@
         <v>61</v>
       </c>
       <c r="B56">
-        <v>0.0016503</v>
+        <v>0.0018949</v>
       </c>
       <c r="C56">
-        <v>0.0011705</v>
+        <v>0.001328</v>
       </c>
       <c r="D56">
-        <v>0.0009863000000000001</v>
+        <v>0.0011934</v>
       </c>
       <c r="E56">
-        <v>0.0007559999999999999</v>
+        <v>0.0008858</v>
       </c>
       <c r="F56">
-        <v>0.0012153</v>
+        <v>0.0013873</v>
       </c>
       <c r="G56">
-        <v>0.00115568</v>
+        <v>0.00133788</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1885,22 +1885,22 @@
         <v>62</v>
       </c>
       <c r="B57">
-        <v>0.0017146</v>
+        <v>0.0019331</v>
       </c>
       <c r="C57">
-        <v>0.0010835</v>
+        <v>0.0013145</v>
       </c>
       <c r="D57">
-        <v>0.0009362999999999999</v>
+        <v>0.0011522</v>
       </c>
       <c r="E57">
-        <v>0.0007329999999999999</v>
+        <v>0.0008629</v>
       </c>
       <c r="F57">
-        <v>0.0011734</v>
+        <v>0.0013487</v>
       </c>
       <c r="G57">
-        <v>0.00112816</v>
+        <v>0.00132228</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1908,22 +1908,22 @@
         <v>63</v>
       </c>
       <c r="B58">
-        <v>0.0018471</v>
+        <v>0.0021371</v>
       </c>
       <c r="C58">
-        <v>0.0012882</v>
+        <v>0.0014689</v>
       </c>
       <c r="D58">
-        <v>0.0013145</v>
+        <v>0.0015903</v>
       </c>
       <c r="E58">
-        <v>0.00126</v>
+        <v>0.0015059</v>
       </c>
       <c r="F58">
-        <v>0.0023144</v>
+        <v>0.002153899999999999</v>
       </c>
       <c r="G58">
-        <v>0.00160484</v>
+        <v>0.00177122</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1931,22 +1931,22 @@
         <v>64</v>
       </c>
       <c r="B59">
-        <v>0.0027614</v>
+        <v>0.0031941</v>
       </c>
       <c r="C59">
-        <v>0.0031521</v>
+        <v>0.003642</v>
       </c>
       <c r="D59">
-        <v>0.0016225</v>
+        <v>0.0018253</v>
       </c>
       <c r="E59">
-        <v>0.0013931</v>
+        <v>0.0015796</v>
       </c>
       <c r="F59">
-        <v>0.0013194</v>
+        <v>0.0015897</v>
       </c>
       <c r="G59">
-        <v>0.0020497</v>
+        <v>0.00236614</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1954,22 +1954,22 @@
         <v>65</v>
       </c>
       <c r="B60">
-        <v>0.0013606</v>
+        <v>0.0016013</v>
       </c>
       <c r="C60">
-        <v>0.0013913</v>
+        <v>0.0013712</v>
       </c>
       <c r="D60">
-        <v>0.0010487</v>
+        <v>0.0011183</v>
       </c>
       <c r="E60">
-        <v>0.0012108</v>
+        <v>0.0012771</v>
       </c>
       <c r="F60">
-        <v>0.0016312</v>
+        <v>0.0024396</v>
       </c>
       <c r="G60">
-        <v>0.00132852</v>
+        <v>0.0015615</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1977,22 +1977,22 @@
         <v>66</v>
       </c>
       <c r="B61">
-        <v>0.0010395</v>
+        <v>0.0011716</v>
       </c>
       <c r="C61">
-        <v>0.0013801</v>
+        <v>0.0015817</v>
       </c>
       <c r="D61">
-        <v>0.0012117</v>
+        <v>0.0013086</v>
       </c>
       <c r="E61">
-        <v>0.0010906</v>
+        <v>0.0013031</v>
       </c>
       <c r="F61">
-        <v>0.0022641</v>
+        <v>0.0025961</v>
       </c>
       <c r="G61">
-        <v>0.0013972</v>
+        <v>0.00159222</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -2000,22 +2000,22 @@
         <v>67</v>
       </c>
       <c r="B62">
-        <v>0.0009938</v>
+        <v>0.0011191</v>
       </c>
       <c r="C62">
-        <v>0.0013852</v>
+        <v>0.0015862</v>
       </c>
       <c r="D62">
-        <v>0.0010638</v>
+        <v>0.0012996</v>
       </c>
       <c r="E62">
-        <v>0.0011071</v>
+        <v>0.0012971</v>
       </c>
       <c r="F62">
-        <v>0.0017042</v>
+        <v>0.002357199999999999</v>
       </c>
       <c r="G62">
-        <v>0.00125082</v>
+        <v>0.00153184</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -2023,22 +2023,22 @@
         <v>68</v>
       </c>
       <c r="B63">
-        <v>0.0010177</v>
+        <v>0.001131</v>
       </c>
       <c r="C63">
-        <v>0.0011687</v>
+        <v>0.0013155</v>
       </c>
       <c r="D63">
-        <v>0.0009733000000000001</v>
+        <v>0.0011079</v>
       </c>
       <c r="E63">
-        <v>0.0009707</v>
+        <v>0.0015866</v>
       </c>
       <c r="F63">
-        <v>0.0016366</v>
+        <v>0.0024307</v>
       </c>
       <c r="G63">
-        <v>0.0011534</v>
+        <v>0.00151434</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -2046,22 +2046,22 @@
         <v>69</v>
       </c>
       <c r="B64">
-        <v>0.0016805</v>
+        <v>0.0019317</v>
       </c>
       <c r="C64">
-        <v>0.0011564</v>
+        <v>0.0013448</v>
       </c>
       <c r="D64">
-        <v>0.0009920999999999999</v>
+        <v>0.0012085</v>
       </c>
       <c r="E64">
-        <v>0.0008776000000000001</v>
+        <v>0.0009185</v>
       </c>
       <c r="F64">
-        <v>0.001227</v>
+        <v>0.0014158</v>
       </c>
       <c r="G64">
-        <v>0.00118672</v>
+        <v>0.00136386</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -2069,22 +2069,22 @@
         <v>70</v>
       </c>
       <c r="B65">
-        <v>0.0012076</v>
+        <v>0.0011567</v>
       </c>
       <c r="C65">
-        <v>0.0014773</v>
+        <v>0.0016311</v>
       </c>
       <c r="D65">
-        <v>0.0010941</v>
+        <v>0.0013618</v>
       </c>
       <c r="E65">
-        <v>0.0012325</v>
+        <v>0.0015026</v>
       </c>
       <c r="F65">
-        <v>0.001875</v>
+        <v>0.0024502</v>
       </c>
       <c r="G65">
-        <v>0.0013773</v>
+        <v>0.00162048</v>
       </c>
     </row>
   </sheetData>
@@ -2367,10 +2367,10 @@
         <v>40</v>
       </c>
       <c r="F12">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G12">
-        <v>43</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2407,7 +2407,7 @@
         <v>44</v>
       </c>
       <c r="D14">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E14">
         <v>40</v>
@@ -2416,7 +2416,7 @@
         <v>46</v>
       </c>
       <c r="G14">
-        <v>46.4</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2585,7 +2585,7 @@
         <v>27</v>
       </c>
       <c r="B22">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C22">
         <v>19</v>
@@ -2600,7 +2600,7 @@
         <v>12</v>
       </c>
       <c r="G22">
-        <v>19.2</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2775,7 +2775,7 @@
         <v>11</v>
       </c>
       <c r="D30">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E30">
         <v>9</v>
@@ -2784,7 +2784,7 @@
         <v>6</v>
       </c>
       <c r="G30">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2936,16 +2936,16 @@
         <v>19</v>
       </c>
       <c r="D37">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E37">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F37">
         <v>16</v>
       </c>
       <c r="G37">
-        <v>18.6</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -3045,7 +3045,7 @@
         <v>47</v>
       </c>
       <c r="B42">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C42">
         <v>19</v>
@@ -3060,7 +3060,7 @@
         <v>12</v>
       </c>
       <c r="G42">
-        <v>19.6</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3068,7 +3068,7 @@
         <v>48</v>
       </c>
       <c r="B43">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C43">
         <v>11</v>
@@ -3083,7 +3083,7 @@
         <v>4</v>
       </c>
       <c r="G43">
-        <v>10.2</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3232,19 +3232,19 @@
         <v>20</v>
       </c>
       <c r="C50">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D50">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E50">
         <v>23</v>
       </c>
       <c r="F50">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G50">
-        <v>19.4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -3327,16 +3327,16 @@
         <v>11</v>
       </c>
       <c r="D54">
+        <v>15</v>
+      </c>
+      <c r="E54">
         <v>9</v>
-      </c>
-      <c r="E54">
-        <v>12</v>
       </c>
       <c r="F54">
         <v>4</v>
       </c>
       <c r="G54">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -3413,7 +3413,7 @@
         <v>63</v>
       </c>
       <c r="B58">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C58">
         <v>11</v>
@@ -3428,7 +3428,7 @@
         <v>4</v>
       </c>
       <c r="G58">
-        <v>10.6</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3462,19 +3462,19 @@
         <v>11</v>
       </c>
       <c r="C60">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D60">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E60">
         <v>11</v>
       </c>
       <c r="F60">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G60">
-        <v>9.199999999999999</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3514,10 +3514,10 @@
         <v>24</v>
       </c>
       <c r="E62">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F62">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G62">
         <v>20.2</v>
@@ -3537,13 +3537,13 @@
         <v>16</v>
       </c>
       <c r="E63">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F63">
         <v>6</v>
       </c>
       <c r="G63">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3583,13 +3583,13 @@
         <v>16</v>
       </c>
       <c r="E65">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F65">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G65">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
     </row>
   </sheetData>
@@ -3872,10 +3872,10 @@
         <v>49.35533905932738</v>
       </c>
       <c r="F12">
-        <v>47.94112549695429</v>
+        <v>47.35533905932738</v>
       </c>
       <c r="G12">
-        <v>50.78132752230962</v>
+        <v>50.66417023478424</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -3906,13 +3906,13 @@
         <v>19</v>
       </c>
       <c r="B14">
-        <v>58.52691193458119</v>
+        <v>59.35533905932739</v>
       </c>
       <c r="C14">
         <v>52.52691193458119</v>
       </c>
       <c r="D14">
-        <v>57.21320343559641</v>
+        <v>57.79898987322334</v>
       </c>
       <c r="E14">
         <v>48.52691193458118</v>
@@ -3921,7 +3921,7 @@
         <v>52.04163056034262</v>
       </c>
       <c r="G14">
-        <v>53.76711395993652</v>
+        <v>54.04995667241114</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -4090,7 +4090,7 @@
         <v>27</v>
       </c>
       <c r="B22">
-        <v>55.69848480983499</v>
+        <v>52.04163056034262</v>
       </c>
       <c r="C22">
         <v>51.69848480983499</v>
@@ -4105,7 +4105,7 @@
         <v>47.35533905932738</v>
       </c>
       <c r="G22">
-        <v>51.06417023478423</v>
+        <v>50.33279938488575</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -4159,7 +4159,7 @@
         <v>30</v>
       </c>
       <c r="B25">
-        <v>57.94112549695429</v>
+        <v>58.76955262170047</v>
       </c>
       <c r="C25">
         <v>52.52691193458119</v>
@@ -4174,7 +4174,7 @@
         <v>48.52691193458118</v>
       </c>
       <c r="G25">
-        <v>52.94701294725886</v>
+        <v>53.11269837220809</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -4274,13 +4274,13 @@
         <v>35</v>
       </c>
       <c r="B30">
-        <v>55.76995750265435</v>
+        <v>56.79900625789294</v>
       </c>
       <c r="C30">
         <v>50.68849900905803</v>
       </c>
       <c r="D30">
-        <v>54.33331983263714</v>
+        <v>55.19395722372492</v>
       </c>
       <c r="E30">
         <v>47.04260386248743</v>
@@ -4289,7 +4289,7 @@
         <v>47.81214177348095</v>
       </c>
       <c r="G30">
-        <v>51.12930439606357</v>
+        <v>51.50724162532885</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -4441,16 +4441,16 @@
         <v>51.69848480983499</v>
       </c>
       <c r="D37">
-        <v>54.38477631085023</v>
+        <v>52.04163056034262</v>
       </c>
       <c r="E37">
-        <v>49.35533905932738</v>
+        <v>48.52691193458118</v>
       </c>
       <c r="F37">
         <v>47.35533905932738</v>
       </c>
       <c r="G37">
-        <v>50.96711395993652</v>
+        <v>50.33279938488575</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -4550,7 +4550,7 @@
         <v>47</v>
       </c>
       <c r="B42">
-        <v>55.69848480983499</v>
+        <v>53.21320343559643</v>
       </c>
       <c r="C42">
         <v>51.69848480983499</v>
@@ -4565,7 +4565,7 @@
         <v>47.35533905932738</v>
       </c>
       <c r="G42">
-        <v>51.06417023478423</v>
+        <v>50.56711395993651</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -4573,7 +4573,7 @@
         <v>48</v>
       </c>
       <c r="B43">
-        <v>54.98590247034177</v>
+        <v>51.32904822084939</v>
       </c>
       <c r="C43">
         <v>50.78481790424926</v>
@@ -4588,7 +4588,7 @@
         <v>47.01219330881975</v>
       </c>
       <c r="G43">
-        <v>50.21248220619938</v>
+        <v>49.4811113563009</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -4596,7 +4596,7 @@
         <v>49</v>
       </c>
       <c r="B44">
-        <v>55.73392301975998</v>
+        <v>56.76297177499858</v>
       </c>
       <c r="C44">
         <v>51.00369305783835</v>
@@ -4611,7 +4611,7 @@
         <v>46.34657557770468</v>
       </c>
       <c r="G44">
-        <v>50.88566928967698</v>
+        <v>51.09147904072469</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -4645,7 +4645,7 @@
         <v>55.69848480983499</v>
       </c>
       <c r="C46">
-        <v>51.69848480983499</v>
+        <v>52.52691193458119</v>
       </c>
       <c r="D46">
         <v>54.04163056034262</v>
@@ -4657,7 +4657,7 @@
         <v>48.52691193458118</v>
       </c>
       <c r="G46">
-        <v>51.69848480983499</v>
+        <v>51.86417023478423</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -4734,22 +4734,22 @@
         <v>55</v>
       </c>
       <c r="B50">
-        <v>71.9411254969543</v>
+        <v>65.11269837220809</v>
       </c>
       <c r="C50">
-        <v>51.69848480983499</v>
+        <v>54.04163056034262</v>
       </c>
       <c r="D50">
-        <v>54.38477631085023</v>
+        <v>52.04163056034262</v>
       </c>
       <c r="E50">
         <v>48.52691193458118</v>
       </c>
       <c r="F50">
-        <v>47.35533905932738</v>
+        <v>49.69848480983499</v>
       </c>
       <c r="G50">
-        <v>54.78132752230961</v>
+        <v>53.8842712474619</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -4812,13 +4812,13 @@
         <v>54.04163056034262</v>
       </c>
       <c r="E53">
-        <v>49.35533905932738</v>
+        <v>48.52691193458118</v>
       </c>
       <c r="F53">
         <v>49.69848480983499</v>
       </c>
       <c r="G53">
-        <v>52.56711395993652</v>
+        <v>52.40142853498728</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -4832,16 +4832,16 @@
         <v>50.21768795326422</v>
       </c>
       <c r="D54">
-        <v>53.36911568474508</v>
+        <v>50.94267710322084</v>
       </c>
       <c r="E54">
-        <v>48.08541237931293</v>
+        <v>47.14260879307493</v>
       </c>
       <c r="F54">
         <v>46.02417147054884</v>
       </c>
       <c r="G54">
-        <v>49.69687530292364</v>
+        <v>49.02302686937119</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -4918,7 +4918,7 @@
         <v>63</v>
       </c>
       <c r="B58">
-        <v>54.98590247034177</v>
+        <v>52.5006210961032</v>
       </c>
       <c r="C58">
         <v>50.78481790424926</v>
@@ -4933,7 +4933,7 @@
         <v>47.01219330881975</v>
       </c>
       <c r="G58">
-        <v>50.21248220619938</v>
+        <v>49.71542593135166</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -4944,7 +4944,7 @@
         <v>55.03558274568525</v>
       </c>
       <c r="C59">
-        <v>49.41629200298021</v>
+        <v>49.69377351010213</v>
       </c>
       <c r="D59">
         <v>52.49710117158692</v>
@@ -4956,7 +4956,7 @@
         <v>46.34657557770468</v>
       </c>
       <c r="G59">
-        <v>50.12032785376795</v>
+        <v>50.17582415519234</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -4964,22 +4964,22 @@
         <v>65</v>
       </c>
       <c r="B60">
-        <v>68.70406320610682</v>
+        <v>56.31376433994424</v>
       </c>
       <c r="C60">
-        <v>50.21768795326422</v>
+        <v>52.28288660312667</v>
       </c>
       <c r="D60">
-        <v>53.36911568474508</v>
+        <v>50.7036069802176</v>
       </c>
       <c r="E60">
-        <v>46.3684244370276</v>
+        <v>46.62036033923231</v>
       </c>
       <c r="F60">
-        <v>46.02417147054884</v>
+        <v>47.71474284512288</v>
       </c>
       <c r="G60">
-        <v>52.93669255033851</v>
+        <v>50.72707222152874</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -5019,13 +5019,13 @@
         <v>54.04163056034262</v>
       </c>
       <c r="E62">
-        <v>49.35533905932738</v>
+        <v>48.52691193458118</v>
       </c>
       <c r="F62">
         <v>49.69848480983499</v>
       </c>
       <c r="G62">
-        <v>52.56711395993652</v>
+        <v>52.40142853498728</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -5042,13 +5042,13 @@
         <v>53.49858672138247</v>
       </c>
       <c r="E63">
-        <v>48.06132626728805</v>
+        <v>46.38680108646078</v>
       </c>
       <c r="F63">
         <v>47.71474284512288</v>
       </c>
       <c r="G63">
-        <v>51.37743494031385</v>
+        <v>51.0425299041484</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -5088,13 +5088,13 @@
         <v>53.49858672138247</v>
       </c>
       <c r="E65">
-        <v>48.06132626728805</v>
+        <v>47.14260879307493</v>
       </c>
       <c r="F65">
-        <v>47.71474284512288</v>
+        <v>47.14611030066301</v>
       </c>
       <c r="G65">
-        <v>51.37743494031385</v>
+        <v>51.07996493657924</v>
       </c>
     </row>
   </sheetData>
@@ -5273,22 +5273,22 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C8">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D8">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E8">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F8">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="G8">
-        <v>97.8</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -5365,22 +5365,22 @@
         <v>17</v>
       </c>
       <c r="B12">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C12">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D12">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E12">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="F12">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="G12">
-        <v>106</v>
+        <v>100.2</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -5411,13 +5411,13 @@
         <v>19</v>
       </c>
       <c r="B14">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C14">
         <v>102</v>
       </c>
       <c r="D14">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E14">
         <v>90</v>
@@ -5426,7 +5426,7 @@
         <v>94</v>
       </c>
       <c r="G14">
-        <v>92.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -5483,7 +5483,7 @@
         <v>78</v>
       </c>
       <c r="C17">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D17">
         <v>54</v>
@@ -5492,10 +5492,10 @@
         <v>107</v>
       </c>
       <c r="F17">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G17">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -5595,13 +5595,13 @@
         <v>27</v>
       </c>
       <c r="B22">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C22">
         <v>13</v>
       </c>
       <c r="D22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E22">
         <v>20</v>
@@ -5610,7 +5610,7 @@
         <v>10</v>
       </c>
       <c r="G22">
-        <v>11.4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -5618,22 +5618,22 @@
         <v>28</v>
       </c>
       <c r="B23">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C23">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D23">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E23">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F23">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="G23">
-        <v>97.8</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -5664,22 +5664,22 @@
         <v>30</v>
       </c>
       <c r="B25">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C25">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D25">
         <v>68</v>
       </c>
       <c r="E25">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F25">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G25">
-        <v>90.2</v>
+        <v>88.2</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -5733,22 +5733,22 @@
         <v>33</v>
       </c>
       <c r="B28">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C28">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D28">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E28">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F28">
         <v>120</v>
       </c>
       <c r="G28">
-        <v>91.2</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -5756,22 +5756,22 @@
         <v>34</v>
       </c>
       <c r="B29">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C29">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D29">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E29">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="F29">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="G29">
-        <v>106</v>
+        <v>100.2</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -5779,13 +5779,13 @@
         <v>35</v>
       </c>
       <c r="B30">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C30">
         <v>102</v>
       </c>
       <c r="D30">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E30">
         <v>90</v>
@@ -5794,7 +5794,7 @@
         <v>94</v>
       </c>
       <c r="G30">
-        <v>92.40000000000001</v>
+        <v>91.59999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -5825,22 +5825,22 @@
         <v>37</v>
       </c>
       <c r="B32">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C32">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D32">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E32">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F32">
         <v>99</v>
       </c>
       <c r="G32">
-        <v>89.2</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -5851,7 +5851,7 @@
         <v>78</v>
       </c>
       <c r="C33">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D33">
         <v>54</v>
@@ -5860,10 +5860,10 @@
         <v>107</v>
       </c>
       <c r="F33">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G33">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -5940,22 +5940,22 @@
         <v>42</v>
       </c>
       <c r="B37">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C37">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D37">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E37">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F37">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G37">
-        <v>19.2</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -6055,7 +6055,7 @@
         <v>47</v>
       </c>
       <c r="B42">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C42">
         <v>16</v>
@@ -6070,7 +6070,7 @@
         <v>13</v>
       </c>
       <c r="G42">
-        <v>15.6</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -6078,13 +6078,13 @@
         <v>48</v>
       </c>
       <c r="B43">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C43">
         <v>13</v>
       </c>
       <c r="D43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E43">
         <v>20</v>
@@ -6093,7 +6093,7 @@
         <v>10</v>
       </c>
       <c r="G43">
-        <v>11.4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -6101,22 +6101,22 @@
         <v>49</v>
       </c>
       <c r="B44">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C44">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D44">
         <v>68</v>
       </c>
       <c r="E44">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F44">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G44">
-        <v>90.2</v>
+        <v>88.2</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -6147,22 +6147,22 @@
         <v>51</v>
       </c>
       <c r="B46">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C46">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D46">
         <v>78</v>
       </c>
       <c r="E46">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F46">
         <v>109</v>
       </c>
       <c r="G46">
-        <v>98.40000000000001</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -6170,22 +6170,22 @@
         <v>52</v>
       </c>
       <c r="B47">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C47">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D47">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E47">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F47">
         <v>120</v>
       </c>
       <c r="G47">
-        <v>91.2</v>
+        <v>89</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -6193,22 +6193,22 @@
         <v>53</v>
       </c>
       <c r="B48">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C48">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D48">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E48">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F48">
         <v>99</v>
       </c>
       <c r="G48">
-        <v>89.2</v>
+        <v>88</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -6242,19 +6242,19 @@
         <v>19</v>
       </c>
       <c r="C50">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D50">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E50">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F50">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G50">
-        <v>17.8</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -6308,22 +6308,22 @@
         <v>58</v>
       </c>
       <c r="B53">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C53">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D53">
         <v>21</v>
       </c>
       <c r="E53">
+        <v>27</v>
+      </c>
+      <c r="F53">
         <v>18</v>
       </c>
-      <c r="F53">
-        <v>14</v>
-      </c>
       <c r="G53">
-        <v>17.2</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -6331,22 +6331,22 @@
         <v>59</v>
       </c>
       <c r="B54">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C54">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D54">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E54">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F54">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G54">
-        <v>19.2</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -6423,7 +6423,7 @@
         <v>63</v>
       </c>
       <c r="B58">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C58">
         <v>16</v>
@@ -6438,7 +6438,7 @@
         <v>13</v>
       </c>
       <c r="G58">
-        <v>15.6</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -6446,22 +6446,22 @@
         <v>64</v>
       </c>
       <c r="B59">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C59">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D59">
         <v>78</v>
       </c>
       <c r="E59">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F59">
         <v>109</v>
       </c>
       <c r="G59">
-        <v>98.40000000000001</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -6472,19 +6472,19 @@
         <v>19</v>
       </c>
       <c r="C60">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D60">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E60">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F60">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G60">
-        <v>17.8</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -6515,19 +6515,19 @@
         <v>67</v>
       </c>
       <c r="B62">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C62">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D62">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E62">
         <v>23</v>
       </c>
       <c r="F62">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G62">
         <v>18.6</v>
@@ -6538,22 +6538,22 @@
         <v>68</v>
       </c>
       <c r="B63">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C63">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D63">
         <v>21</v>
       </c>
       <c r="E63">
+        <v>27</v>
+      </c>
+      <c r="F63">
         <v>18</v>
       </c>
-      <c r="F63">
-        <v>14</v>
-      </c>
       <c r="G63">
-        <v>17.2</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -6584,19 +6584,19 @@
         <v>70</v>
       </c>
       <c r="B65">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C65">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D65">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E65">
         <v>23</v>
       </c>
       <c r="F65">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G65">
         <v>18.6</v>
@@ -6870,22 +6870,22 @@
         <v>17</v>
       </c>
       <c r="B12">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C12">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D12">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E12">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F12">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="G12">
-        <v>209.8</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -6916,13 +6916,13 @@
         <v>19</v>
       </c>
       <c r="B14">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="C14">
         <v>92</v>
       </c>
       <c r="D14">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E14">
         <v>50</v>
@@ -6931,7 +6931,7 @@
         <v>48</v>
       </c>
       <c r="G14">
-        <v>99.40000000000001</v>
+        <v>101.8</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -7100,10 +7100,10 @@
         <v>27</v>
       </c>
       <c r="B22">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C22">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D22">
         <v>59</v>
@@ -7115,7 +7115,7 @@
         <v>29</v>
       </c>
       <c r="G22">
-        <v>50.2</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -7169,10 +7169,10 @@
         <v>30</v>
       </c>
       <c r="B25">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="C25">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D25">
         <v>102</v>
@@ -7184,7 +7184,7 @@
         <v>57</v>
       </c>
       <c r="G25">
-        <v>104.6</v>
+        <v>107</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -7241,13 +7241,13 @@
         <v>208</v>
       </c>
       <c r="C28">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D28">
         <v>129</v>
       </c>
       <c r="E28">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F28">
         <v>172</v>
@@ -7261,22 +7261,22 @@
         <v>34</v>
       </c>
       <c r="B29">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C29">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D29">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E29">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F29">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="G29">
-        <v>209.8</v>
+        <v>208</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -7284,13 +7284,13 @@
         <v>35</v>
       </c>
       <c r="B30">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="C30">
         <v>92</v>
       </c>
       <c r="D30">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E30">
         <v>50</v>
@@ -7299,7 +7299,7 @@
         <v>48</v>
       </c>
       <c r="G30">
-        <v>99.40000000000001</v>
+        <v>101.8</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -7336,16 +7336,16 @@
         <v>117</v>
       </c>
       <c r="D32">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E32">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F32">
         <v>47</v>
       </c>
       <c r="G32">
-        <v>101</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -7445,22 +7445,22 @@
         <v>42</v>
       </c>
       <c r="B37">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C37">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D37">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E37">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F37">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G37">
-        <v>37.2</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -7560,7 +7560,7 @@
         <v>47</v>
       </c>
       <c r="B42">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C42">
         <v>45</v>
@@ -7572,10 +7572,10 @@
         <v>50</v>
       </c>
       <c r="F42">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G42">
-        <v>46</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -7583,10 +7583,10 @@
         <v>48</v>
       </c>
       <c r="B43">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C43">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D43">
         <v>59</v>
@@ -7598,7 +7598,7 @@
         <v>29</v>
       </c>
       <c r="G43">
-        <v>50.2</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -7606,10 +7606,10 @@
         <v>49</v>
       </c>
       <c r="B44">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="C44">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D44">
         <v>102</v>
@@ -7621,7 +7621,7 @@
         <v>57</v>
       </c>
       <c r="G44">
-        <v>104.6</v>
+        <v>107</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -7652,22 +7652,22 @@
         <v>51</v>
       </c>
       <c r="B46">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C46">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D46">
         <v>93</v>
       </c>
       <c r="E46">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F46">
         <v>65</v>
       </c>
       <c r="G46">
-        <v>115.2</v>
+        <v>115.6</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -7678,13 +7678,13 @@
         <v>208</v>
       </c>
       <c r="C47">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D47">
         <v>129</v>
       </c>
       <c r="E47">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F47">
         <v>172</v>
@@ -7704,16 +7704,16 @@
         <v>117</v>
       </c>
       <c r="D48">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E48">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F48">
         <v>47</v>
       </c>
       <c r="G48">
-        <v>101</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -7744,22 +7744,22 @@
         <v>55</v>
       </c>
       <c r="B50">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C50">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D50">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E50">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F50">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G50">
-        <v>32.8</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -7813,22 +7813,22 @@
         <v>58</v>
       </c>
       <c r="B53">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C53">
+        <v>41</v>
+      </c>
+      <c r="D53">
         <v>39</v>
       </c>
-      <c r="D53">
-        <v>37</v>
-      </c>
       <c r="E53">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="F53">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G53">
-        <v>32</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -7836,22 +7836,22 @@
         <v>59</v>
       </c>
       <c r="B54">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C54">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D54">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E54">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F54">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G54">
-        <v>37.2</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -7928,7 +7928,7 @@
         <v>63</v>
       </c>
       <c r="B58">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C58">
         <v>45</v>
@@ -7940,10 +7940,10 @@
         <v>50</v>
       </c>
       <c r="F58">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G58">
-        <v>46</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -7951,22 +7951,22 @@
         <v>64</v>
       </c>
       <c r="B59">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C59">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D59">
         <v>93</v>
       </c>
       <c r="E59">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F59">
         <v>65</v>
       </c>
       <c r="G59">
-        <v>115.2</v>
+        <v>115.6</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -7974,22 +7974,22 @@
         <v>65</v>
       </c>
       <c r="B60">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C60">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D60">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E60">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F60">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G60">
-        <v>32.8</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -8020,22 +8020,22 @@
         <v>67</v>
       </c>
       <c r="B62">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C62">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D62">
+        <v>39</v>
+      </c>
+      <c r="E62">
         <v>37</v>
       </c>
-      <c r="E62">
-        <v>38</v>
-      </c>
       <c r="F62">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G62">
-        <v>33.4</v>
+        <v>33</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -8043,22 +8043,22 @@
         <v>68</v>
       </c>
       <c r="B63">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C63">
+        <v>41</v>
+      </c>
+      <c r="D63">
         <v>39</v>
       </c>
-      <c r="D63">
-        <v>37</v>
-      </c>
       <c r="E63">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="F63">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G63">
-        <v>32</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -8089,22 +8089,22 @@
         <v>70</v>
       </c>
       <c r="B65">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C65">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D65">
+        <v>39</v>
+      </c>
+      <c r="E65">
         <v>37</v>
       </c>
-      <c r="E65">
-        <v>38</v>
-      </c>
       <c r="F65">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G65">
-        <v>33.4</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -8387,10 +8387,10 @@
         <v>16</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G12">
-        <v>12</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -8421,13 +8421,13 @@
         <v>19</v>
       </c>
       <c r="B14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C14">
         <v>12</v>
       </c>
       <c r="D14">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E14">
         <v>10</v>
@@ -8436,7 +8436,7 @@
         <v>7</v>
       </c>
       <c r="G14">
-        <v>12.8</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -8605,7 +8605,7 @@
         <v>27</v>
       </c>
       <c r="B22">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C22">
         <v>11</v>
@@ -8620,7 +8620,7 @@
         <v>3</v>
       </c>
       <c r="G22">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -8674,7 +8674,7 @@
         <v>30</v>
       </c>
       <c r="B25">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C25">
         <v>11</v>
@@ -8689,7 +8689,7 @@
         <v>8</v>
       </c>
       <c r="G25">
-        <v>12.2</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -8795,7 +8795,7 @@
         <v>9</v>
       </c>
       <c r="D30">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E30">
         <v>7</v>
@@ -8804,7 +8804,7 @@
         <v>4</v>
       </c>
       <c r="G30">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -8956,16 +8956,16 @@
         <v>12</v>
       </c>
       <c r="D37">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E37">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F37">
         <v>4</v>
       </c>
       <c r="G37">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -9065,7 +9065,7 @@
         <v>47</v>
       </c>
       <c r="B42">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C42">
         <v>11</v>
@@ -9080,7 +9080,7 @@
         <v>3</v>
       </c>
       <c r="G42">
-        <v>10.4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -9088,7 +9088,7 @@
         <v>48</v>
       </c>
       <c r="B43">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C43">
         <v>9</v>
@@ -9103,7 +9103,7 @@
         <v>2</v>
       </c>
       <c r="G43">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -9160,7 +9160,7 @@
         <v>10</v>
       </c>
       <c r="C46">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D46">
         <v>20</v>
@@ -9172,7 +9172,7 @@
         <v>6</v>
       </c>
       <c r="G46">
-        <v>11.6</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -9249,22 +9249,22 @@
         <v>55</v>
       </c>
       <c r="B50">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C50">
+        <v>14</v>
+      </c>
+      <c r="D50">
         <v>12</v>
-      </c>
-      <c r="D50">
-        <v>8</v>
       </c>
       <c r="E50">
         <v>12</v>
       </c>
       <c r="F50">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G50">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -9347,16 +9347,16 @@
         <v>9</v>
       </c>
       <c r="D54">
+        <v>13</v>
+      </c>
+      <c r="E54">
         <v>7</v>
-      </c>
-      <c r="E54">
-        <v>10</v>
       </c>
       <c r="F54">
         <v>2</v>
       </c>
       <c r="G54">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -9433,7 +9433,7 @@
         <v>63</v>
       </c>
       <c r="B58">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C58">
         <v>9</v>
@@ -9448,7 +9448,7 @@
         <v>2</v>
       </c>
       <c r="G58">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -9485,16 +9485,16 @@
         <v>9</v>
       </c>
       <c r="D60">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E60">
         <v>9</v>
       </c>
       <c r="F60">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G60">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -9534,10 +9534,10 @@
         <v>16</v>
       </c>
       <c r="E62">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F62">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G62">
         <v>11.6</v>
@@ -9557,13 +9557,13 @@
         <v>14</v>
       </c>
       <c r="E63">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F63">
         <v>4</v>
       </c>
       <c r="G63">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -9603,13 +9603,13 @@
         <v>14</v>
       </c>
       <c r="E65">
+        <v>7</v>
+      </c>
+      <c r="F65">
+        <v>5</v>
+      </c>
+      <c r="G65">
         <v>9</v>
-      </c>
-      <c r="F65">
-        <v>4</v>
-      </c>
-      <c r="G65">
-        <v>9.199999999999999</v>
       </c>
     </row>
   </sheetData>
